--- a/dev-docs/task-260902-报价与核价建表与导入方案新规范/核价1 - 数据导入与表格建表.xlsx
+++ b/dev-docs/task-260902-报价与核价建表与导入方案新规范/核价1 - 数据导入与表格建表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\.claude\worktrees\task-260819-sql-view-builder\dev-docs\task-260902-报价与核价建表与导入方案新规范\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\dev-docs\task-260902-报价与核价建表与导入方案新规范\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD75F78-1B74-4BBF-A3C0-919654FEDEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB2CEE8-DD66-4D03-AF51-19EEA2B8E039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="909" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="405" yWindow="840" windowWidth="28395" windowHeight="14640" tabRatio="909" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="物料" sheetId="1" r:id="rId1"/>
@@ -962,6 +962,9 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="F2">
+        <v>33</v>
+      </c>
       <c r="G2" s="28" t="s">
         <v>111</v>
       </c>
